--- a/漢字（かんじ）/t.xlsx
+++ b/漢字（かんじ）/t.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="た" sheetId="1" r:id="rId1"/>
@@ -676,7 +676,10 @@
     <t>所得｜しょとく
 所得税｜しょとくぜい
 納得｜なっとく
-得意｜とくい</t>
+得意｜とくい
+修得｜しゅうとく
+習得｜しゅうとく
+取得｜しゅとく</t>
   </si>
   <si>
     <t>登</t>
@@ -845,7 +848,8 @@
   <si>
     <t>投稿｜とうこう
 投入｜とうにゅう
-投棄｜とうき</t>
+投棄｜とうき
+投書｜とうしょ</t>
   </si>
   <si>
     <t>筒</t>
@@ -924,7 +928,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -962,13 +966,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1418,148 +1415,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2761,7 +2758,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="4" ht="72" spans="1:8">
+    <row r="4" ht="126" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>153</v>
       </c>
@@ -2948,7 +2945,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" ht="54" spans="1:8">
+    <row r="16" ht="72" spans="1:8">
       <c r="A16" t="s">
         <v>180</v>
       </c>

--- a/漢字（かんじ）/t.xlsx
+++ b/漢字（かんじ）/t.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="た" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="223">
   <si>
     <t>仮名</t>
   </si>
@@ -540,7 +540,8 @@
   </si>
   <si>
     <t>提出｜ていしゅつ
-提供｜ていきょう</t>
+提供｜ていきょう
+提案｜ていあん</t>
   </si>
   <si>
     <t>抵</t>
@@ -903,6 +904,12 @@
   </si>
   <si>
     <t>祈禱｜きとう</t>
+  </si>
+  <si>
+    <t>闘</t>
+  </si>
+  <si>
+    <t>健闘｜けんとう</t>
   </si>
   <si>
     <t>とん</t>
@@ -2564,7 +2571,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" ht="36" spans="1:3">
+    <row r="15" ht="54" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>130</v>
       </c>
@@ -2691,7 +2698,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="31.7777777777778" customWidth="1"/>
@@ -3033,26 +3040,37 @@
         <v>216</v>
       </c>
     </row>
-    <row r="24" ht="18" spans="1:3">
+    <row r="24" ht="19.2" customHeight="1" spans="1:3">
       <c r="A24" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="1" t="s">
+    </row>
+    <row r="25" ht="18" spans="1:3">
+      <c r="A25" s="1" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="25" ht="36" spans="1:3">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" ht="36" spans="1:3">
+      <c r="A26" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>220</v>
+      <c r="C26" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/t.xlsx
+++ b/漢字（かんじ）/t.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="た" sheetId="1" r:id="rId1"/>
@@ -452,6 +452,7 @@
 天然｜てんねん
 天然水｜てんねんすい
 天井｜てんじょう
+天皇｜てんのう
 摩天楼｜まてんろう
 天変地異｜てんぺんちい</t>
   </si>
@@ -2450,7 +2451,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" ht="108" spans="1:3">
+    <row r="4" ht="126" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>104</v>
       </c>

--- a/漢字（かんじ）/t.xlsx
+++ b/漢字（かんじ）/t.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="た" sheetId="1" r:id="rId1"/>
@@ -230,7 +230,9 @@
     <t>たつ</t>
   </si>
   <si>
-    <t>配達｜はいたつ
+    <t>達成｜たっせい
+達成率｜たっせいりつ
+配達｜はいたつ
 伝達｜でんたつ
 速達｜そくたつ
 発達｜はったつ
@@ -2151,7 +2153,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" ht="126" spans="1:7">
+    <row r="13" ht="162" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>43</v>
       </c>

--- a/漢字（かんじ）/t.xlsx
+++ b/漢字（かんじ）/t.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="225">
   <si>
     <t>仮名</t>
   </si>
@@ -545,6 +545,13 @@
     <t>提出｜ていしゅつ
 提供｜ていきょう
 提案｜ていあん</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>低温｜ていおん
+低音｜ていおん</t>
   </si>
   <si>
     <t>抵</t>
@@ -2412,7 +2419,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -2596,7 +2603,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" ht="36" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>130</v>
       </c>
@@ -2607,7 +2614,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="18" ht="54" spans="1:3">
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
         <v>130</v>
       </c>
@@ -2618,7 +2625,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" ht="180" spans="1:3">
+    <row r="19" ht="54" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>130</v>
       </c>
@@ -2629,7 +2636,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="20" ht="19.8" customHeight="1" spans="1:3">
+    <row r="20" ht="180" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>130</v>
       </c>
@@ -2640,7 +2647,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="21" ht="108" spans="1:3">
+    <row r="21" ht="19.8" customHeight="1" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>130</v>
       </c>
@@ -2651,45 +2658,56 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" ht="19.8" customHeight="1" spans="1:3">
+    <row r="22" ht="108" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="23" ht="54" spans="1:3">
+      <c r="C22" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" ht="19.8" customHeight="1" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B23" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="2" t="s">
+    </row>
+    <row r="24" ht="54" spans="1:3">
+      <c r="A24" s="1" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="25" ht="36" spans="1:3">
+    <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>152</v>
+      </c>
+    </row>
+    <row r="26" ht="36" spans="1:3">
+      <c r="A26" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2730,19 +2748,19 @@
     </row>
     <row r="2" ht="54" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>18</v>
@@ -2750,151 +2768,151 @@
     </row>
     <row r="3" ht="105.6" customHeight="1" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" ht="126" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" ht="31.8" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" ht="36" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" ht="31.2" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" ht="37.2" customHeight="1" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="1"/>
@@ -2902,178 +2920,178 @@
     </row>
     <row r="11" ht="36" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" ht="36" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" ht="108" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" ht="72" spans="1:8">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" ht="72" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" ht="54" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" ht="36" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" ht="36" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" ht="97.8" customHeight="1" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" ht="19.2" customHeight="1" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" ht="19.2" customHeight="1" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" ht="36" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
